--- a/AAII_Financials/Yearly/CISS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CISS_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="92">
   <si>
     <t>CISS</t>
   </si>
@@ -662,8 +662,8 @@
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -693,8 +693,8 @@
       <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>3</v>
+      <c r="H7" s="2">
+        <v>44561</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>3</v>
@@ -729,8 +729,8 @@
       <c r="G8" s="3">
         <v>7900</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
+      <c r="H8" s="3">
+        <v>7500</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>3</v>
@@ -765,8 +765,8 @@
       <c r="G9" s="3">
         <v>1400</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
+      <c r="H9" s="3">
+        <v>400</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>3</v>
@@ -801,8 +801,8 @@
       <c r="G10" s="3">
         <v>6500</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
+      <c r="H10" s="3">
+        <v>7100</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>3</v>
@@ -962,7 +962,7 @@
         <v>1300</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="I15" s="3">
         <v>0</v>
@@ -1010,8 +1010,8 @@
       <c r="G17" s="3">
         <v>6600</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
+      <c r="H17" s="3">
+        <v>3100</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>3</v>
@@ -1046,8 +1046,8 @@
       <c r="G18" s="3">
         <v>1300</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
+      <c r="H18" s="3">
+        <v>4400</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>3</v>
@@ -1098,8 +1098,8 @@
       <c r="G20" s="3">
         <v>0</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
+      <c r="H20" s="3">
+        <v>0</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
@@ -1135,7 +1135,7 @@
         <v>2700</v>
       </c>
       <c r="H21" s="3">
-        <v>0</v>
+        <v>4900</v>
       </c>
       <c r="I21" s="3">
         <v>0</v>
@@ -1170,8 +1170,8 @@
       <c r="G22" s="3">
         <v>0</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
+      <c r="H22" s="3">
+        <v>0</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
@@ -1206,8 +1206,8 @@
       <c r="G23" s="3">
         <v>1300</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
+      <c r="H23" s="3">
+        <v>4300</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>3</v>
@@ -1314,8 +1314,8 @@
       <c r="G26" s="3">
         <v>1300</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
+      <c r="H26" s="3">
+        <v>4300</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>3</v>
@@ -1350,8 +1350,8 @@
       <c r="G27" s="3">
         <v>1300</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
+      <c r="H27" s="3">
+        <v>4300</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>3</v>
@@ -1530,8 +1530,8 @@
       <c r="G32" s="3">
         <v>0</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
+      <c r="H32" s="3">
+        <v>0</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
@@ -1566,8 +1566,8 @@
       <c r="G33" s="3">
         <v>1300</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
+      <c r="H33" s="3">
+        <v>4300</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>3</v>
@@ -1638,8 +1638,8 @@
       <c r="G35" s="3">
         <v>1300</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
+      <c r="H35" s="3">
+        <v>4300</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>3</v>
@@ -1679,8 +1679,8 @@
       <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>3</v>
+      <c r="H38" s="2">
+        <v>44561</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>3</v>
@@ -1747,8 +1747,8 @@
       <c r="G41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
+      <c r="H41" s="3">
+        <v>0</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>3</v>
@@ -1819,8 +1819,8 @@
       <c r="G43" s="3">
         <v>800</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
+      <c r="H43" s="3">
+        <v>4300</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
@@ -1855,8 +1855,8 @@
       <c r="G44" s="3">
         <v>200</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
+      <c r="H44" s="3">
+        <v>100</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>3</v>
@@ -1891,8 +1891,8 @@
       <c r="G45" s="3">
         <v>0</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
+      <c r="H45" s="3">
+        <v>0</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
@@ -1927,8 +1927,8 @@
       <c r="G46" s="3">
         <v>1000</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
+      <c r="H46" s="3">
+        <v>4600</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>3</v>
@@ -1999,8 +1999,8 @@
       <c r="G48" s="3">
         <v>38800</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
+      <c r="H48" s="3">
+        <v>11200</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
@@ -2035,8 +2035,8 @@
       <c r="G49" s="3">
         <v>0</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
+      <c r="H49" s="3">
+        <v>0</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>3</v>
@@ -2143,8 +2143,8 @@
       <c r="G52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
+      <c r="H52" s="3">
+        <v>500</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
@@ -2215,8 +2215,8 @@
       <c r="G54" s="3">
         <v>39900</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
+      <c r="H54" s="3">
+        <v>16400</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>3</v>
@@ -2283,8 +2283,8 @@
       <c r="G57" s="3">
         <v>800</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
+      <c r="H57" s="3">
+        <v>200</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
@@ -2319,8 +2319,8 @@
       <c r="G58" s="3">
         <v>0</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
+      <c r="H58" s="3">
+        <v>1000</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
@@ -2391,8 +2391,8 @@
       <c r="G60" s="3">
         <v>1000</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
+      <c r="H60" s="3">
+        <v>1300</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>3</v>
@@ -2428,7 +2428,7 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>6300</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -2607,8 +2607,8 @@
       <c r="G66" s="3">
         <v>1000</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
+      <c r="H66" s="3">
+        <v>7600</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>3</v>
@@ -2803,8 +2803,8 @@
       <c r="G72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
+      <c r="H72" s="3">
+        <v>3600</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
@@ -2947,8 +2947,8 @@
       <c r="G76" s="3">
         <v>38900</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
+      <c r="H76" s="3">
+        <v>8800</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>3</v>
@@ -3024,8 +3024,8 @@
       <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2" t="s">
-        <v>3</v>
+      <c r="H80" s="2">
+        <v>44561</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>3</v>
@@ -3060,8 +3060,8 @@
       <c r="G81" s="3">
         <v>1300</v>
       </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
+      <c r="H81" s="3">
+        <v>4300</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>3</v>
@@ -3112,8 +3112,8 @@
       <c r="G83" s="3">
         <v>1300</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
+      <c r="H83" s="3">
+        <v>500</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>3</v>
@@ -3328,8 +3328,8 @@
       <c r="G89" s="3">
         <v>2500</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
+      <c r="H89" s="3">
+        <v>0</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>3</v>
@@ -3380,8 +3380,8 @@
       <c r="G91" s="3">
         <v>-39400</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
+      <c r="H91" s="3">
+        <v>-11600</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>3</v>
@@ -3488,8 +3488,8 @@
       <c r="G94" s="3">
         <v>-39400</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
+      <c r="H94" s="3">
+        <v>-11600</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>3</v>
@@ -3684,8 +3684,8 @@
       <c r="G100" s="3">
         <v>92000</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
+      <c r="H100" s="3">
+        <v>14900</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>3</v>
@@ -3757,7 +3757,7 @@
         <v>55200</v>
       </c>
       <c r="H102" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="I102" s="3">
         <v>0</v>
